--- a/Apriori mapp/apriori_results.xlsx
+++ b/Apriori mapp/apriori_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,271 +456,169 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H
+AND SMS received O-S-H=verymanysmsrec_O-S-H</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>SMS sent O-S-H=verymanysmssent_O-S-H</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SMS received O-S-H=verymanysmsrec_O-S-H</t>
-        </is>
-      </c>
       <c r="C2" t="n">
-        <v>0.1205357142857143</v>
+        <v>0.1026785714285714</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9418604651162792</v>
+        <v>0.9452054794520547</v>
       </c>
       <c r="E2" t="n">
-        <v>7.192389006342495</v>
+        <v>7.3857916533928</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SMS received O-S-H=verymanysmsrec_O-S-H</t>
+          <t>SMS sent O-S-H=verymanysmssent_O-S-H</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SMS sent O-S-H=verymanysmssent_O-S-H</t>
+          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H
+AND SMS received O-S-H=verymanysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1205357142857143</v>
+        <v>0.1026785714285714</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9204545454545454</v>
+        <v>0.8023255813953488</v>
       </c>
       <c r="E3" t="n">
-        <v>7.192389006342495</v>
+        <v>7.3857916533928</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SMS conversation S-H=verymanysmsconv_S-H</t>
+          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H
+AND SMS sent O-S-H=verymanysmssent_O-S-H</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMS sent S-H=verymanysmssent_S-H</t>
+          <t>SMS received O-S-H=verymanysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1056547619047619</v>
+        <v>0.1026785714285714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8658536585365854</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="E4" t="n">
-        <v>6.76574021554169</v>
+        <v>7.318181818181818</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SMS sent S-H=verymanysmssent_S-H</t>
+          <t>SMS received O-S-H=verymanysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMS conversation S-H=verymanysmsconv_S-H</t>
+          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H
+AND SMS sent O-S-H=verymanysmssent_O-S-H</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1056547619047619</v>
+        <v>0.1026785714285714</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8255813953488372</v>
+        <v>0.7840909090909091</v>
       </c>
       <c r="E5" t="n">
-        <v>6.76574021554169</v>
+        <v>7.318181818181818</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SMS conversation S-H=verymanysmsconv_S-H</t>
+          <t>SMS received O-S-H=verymanysmsrec_O-S-H
+AND SMS sent O-S-H=verymanysmssent_O-S-H</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMS received S-H=verymanysmsrec_S-H</t>
+          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1056547619047619</v>
+        <v>0.1026785714285714</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8658536585365854</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="E6" t="n">
-        <v>6.537681556590846</v>
+        <v>6.360493827160494</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SMS received S-H=verymanysmsrec_S-H</t>
+          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMS conversation S-H=verymanysmsconv_S-H</t>
+          <t>SMS received O-S-H=verymanysmsrec_O-S-H
+AND SMS sent O-S-H=verymanysmssent_O-S-H</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1056547619047619</v>
+        <v>0.1026785714285714</v>
       </c>
       <c r="D7" t="n">
-        <v>0.797752808988764</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="E7" t="n">
-        <v>6.537681556590846</v>
+        <v>6.360493827160493</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SMS sent S-H=verymanysmssent_S-H</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SMS received S-H=verymanysmsrec_S-H</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.1101190476190476</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.8604651162790699</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6.496995035275673</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SMS received S-H=verymanysmsrec_S-H</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SMS sent S-H=verymanysmssent_S-H</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1101190476190476</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.8314606741573033</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6.496995035275673</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SMS received O-S-H=veryfewsmsrec_O-S-H</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SMS sent O-S-H=veryfewsmssent_O-S-H</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1011904761904762</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.6938775510204082</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.483516483516484</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SMS sent O-S-H=veryfewsmssent_O-S-H</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SMS received O-S-H=veryfewsmsrec_O-S-H</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1011904761904762</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4.483516483516484</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Apriori mapp/apriori_results.xlsx
+++ b/Apriori mapp/apriori_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Leverage count</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Rule length</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Support count</t>
         </is>
@@ -456,169 +466,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H
-AND SMS received O-S-H=verymanysmsrec_O-S-H</t>
+          <t>BT_Outsiders S-H=manybtout_S-H
+ AND BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SMS sent O-S-H=verymanysmssent_O-S-H</t>
+          <t>BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS received O-S-H=manysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1026785714285714</v>
+        <v>0.05208333333333334</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9452054794520547</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3857916533928</v>
+        <v>10.18181818181818</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0.04696800595238095</v>
       </c>
       <c r="G2" t="n">
-        <v>69</v>
+        <v>32</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SMS sent O-S-H=verymanysmssent_O-S-H</t>
+          <t>BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS received O-S-H=manysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H
-AND SMS received O-S-H=verymanysmsrec_O-S-H</t>
+          <t>BT_Outsiders S-H=manybtout_S-H
+ AND BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1026785714285714</v>
+        <v>0.05208333333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3857916533928</v>
+        <v>10.18181818181818</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0.04696800595238095</v>
       </c>
       <c r="G3" t="n">
-        <v>69</v>
+        <v>32</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H
-AND SMS sent O-S-H=verymanysmssent_O-S-H</t>
+          <t>BT_Outsiders S-H=manybtout_S-H
+ AND BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS received O-S-H=manysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMS received O-S-H=verymanysmsrec_O-S-H</t>
+          <t>BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1026785714285714</v>
+        <v>0.05208333333333334</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9210526315789475</v>
       </c>
       <c r="E4" t="n">
-        <v>7.318181818181818</v>
+        <v>10.14667817083693</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0.04695029053287982</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
+        <v>32</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SMS received O-S-H=verymanysmsrec_O-S-H</t>
+          <t>BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H
-AND SMS sent O-S-H=verymanysmssent_O-S-H</t>
+          <t>BT_Outsiders S-H=manybtout_S-H
+ AND BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS received O-S-H=manysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1026785714285714</v>
+        <v>0.05208333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7840909090909091</v>
+        <v>0.5737704918032788</v>
       </c>
       <c r="E5" t="n">
-        <v>7.318181818181818</v>
+        <v>10.14667817083693</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0.04695029053287982</v>
       </c>
       <c r="G5" t="n">
-        <v>69</v>
+        <v>32</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SMS received O-S-H=verymanysmsrec_O-S-H
-AND SMS sent O-S-H=verymanysmssent_O-S-H</t>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS conversation O-S-H=manysmsconv_O-S-H
+ AND SMS received O-S-H=manysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H</t>
+          <t>BT_Average Duration O-S-H=middlebtavgdur_O-S-H
+ AND BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1026785714285714</v>
+        <v>0.0505952380952381</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="E6" t="n">
-        <v>6.360493827160494</v>
+        <v>9.764102564102565</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0.04541347789115646</v>
       </c>
       <c r="G6" t="n">
-        <v>69</v>
+        <v>31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SMS conversation O-S-H=verymanysmsconv_O-S-H</t>
+          <t>BT_Average Duration O-S-H=middlebtavgdur_O-S-H
+ AND BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMS received O-S-H=verymanysmsrec_O-S-H
-AND SMS sent O-S-H=verymanysmssent_O-S-H</t>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS conversation O-S-H=manysmsconv_O-S-H
+ AND SMS received O-S-H=manysmsrec_O-S-H</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1026785714285714</v>
+        <v>0.0505952380952381</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E7" t="n">
-        <v>6.360493827160493</v>
+        <v>9.764102564102563</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0.04541347789115646</v>
       </c>
       <c r="G7" t="n">
-        <v>69</v>
+        <v>31</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BT_Average Duration O-S-H=middlebtavgdur_O-S-H
+ AND BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS received O-S-H=manysmsrec_O-S-H</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS conversation O-S-H=manysmsconv_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0505952380952381</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9.681355932203392</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04536918934240363</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS conversation O-S-H=manysmsconv_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BT_Average Duration O-S-H=middlebtavgdur_O-S-H
+ AND BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS received O-S-H=manysmsrec_O-S-H</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0505952380952381</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.576271186440678</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9.68135593220339</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.04536918934240363</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS received S-H=manysmsrec_S-H</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SMS conversation S-H=manysmsconv_S-H
+ AND SMS sent S-H=manysmssent_S-H</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0505952380952381</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9.520000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.04528061224489796</v>
+      </c>
+      <c r="G10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SMS conversation S-H=manysmsconv_S-H
+ AND SMS sent S-H=manysmssent_S-H</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS received S-H=manysmsrec_S-H</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0505952380952381</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.04528061224489796</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Apriori mapp/apriori_results.xlsx
+++ b/Apriori mapp/apriori_results.xlsx
@@ -466,216 +466,202 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BT_Outsiders S-H=manybtout_S-H
- AND BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS sent O-S-H=manysmssent_O-S-H</t>
+          <t>SMS unique people S-H=manysmsunq_S-H</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BT_Interactions O-S-H=manybtint_O-S-H
- AND SMS received O-S-H=manysmsrec_O-S-H</t>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND Calls Unique People S-H=manycallsunq_S-H</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.0505952380952381</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5074626865671642</v>
       </c>
       <c r="E2" t="n">
-        <v>10.18181818181818</v>
+        <v>5.779913989375159</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04696800595238095</v>
+        <v>0.04184160643424036</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BT_Interactions O-S-H=manybtint_O-S-H
- AND SMS received O-S-H=manysmsrec_O-S-H</t>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND Calls Unique People S-H=manycallsunq_S-H</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BT_Outsiders S-H=manybtout_S-H
- AND BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS sent O-S-H=manysmssent_O-S-H</t>
+          <t>SMS unique people S-H=manysmsunq_S-H</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.0505952380952381</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="E3" t="n">
-        <v>10.18181818181818</v>
+        <v>5.779913989375158</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04696800595238095</v>
+        <v>0.04184160643424036</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT_Outsiders S-H=manybtout_S-H
- AND BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS received O-S-H=manysmsrec_O-S-H</t>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS unique people S-H=manysmsunq_S-H</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BT_Interactions O-S-H=manybtint_O-S-H
- AND SMS sent O-S-H=manysmssent_O-S-H</t>
+          <t>Calls Unique People S-H=manycallsunq_S-H</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.0505952380952381</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9210526315789475</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>10.14667817083693</v>
+        <v>5.44</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04695029053287982</v>
+        <v>0.04129464285714286</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>SMS unique people O-S-H=manysmsunq_O-S-H</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>BT_Interactions O-S-H=manybtint_O-S-H
- AND SMS sent O-S-H=manysmssent_O-S-H</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BT_Outsiders S-H=manybtout_S-H
- AND BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS received O-S-H=manysmsrec_O-S-H</t>
+ AND fb=verymanyfb</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.0505952380952381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5737704918032788</v>
+        <v>0.53125</v>
       </c>
       <c r="E5" t="n">
-        <v>10.14667817083693</v>
+        <v>5.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04695029053287982</v>
+        <v>0.04067460317460318</v>
       </c>
       <c r="G5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>SMS unique people O-S-H=manysmsunq_O-S-H</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS conversation O-S-H=manysmsconv_O-S-H
- AND SMS received O-S-H=manysmsrec_O-S-H</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BT_Average Duration O-S-H=middlebtavgdur_O-S-H
- AND BT_Interactions O-S-H=manybtint_O-S-H
- AND SMS sent O-S-H=manysmssent_O-S-H</t>
+ AND fb=verymanyfb</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0505952380952381</v>
+        <v>0.05208333333333334</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.546875</v>
       </c>
       <c r="E6" t="n">
-        <v>9.764102564102565</v>
+        <v>4.966216216216217</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04541347789115646</v>
+        <v>0.04159580498866214</v>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BT_Average Duration O-S-H=middlebtavgdur_O-S-H
- AND BT_Interactions O-S-H=manybtint_O-S-H
- AND SMS sent O-S-H=manysmssent_O-S-H</t>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND Calls Duration O-S-H=veryhighcalldur_O-S-H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS conversation O-S-H=manysmsconv_O-S-H
- AND SMS received O-S-H=manysmsrec_O-S-H</t>
+          <t>SMS sent O-S-H=manysmssent_O-S-H</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0.0505952380952381</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="E7" t="n">
-        <v>9.764102564102563</v>
+        <v>4.393846153846154</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04541347789115646</v>
+        <v>0.03908021541950114</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>34</v>
@@ -684,35 +670,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BT_Average Duration O-S-H=middlebtavgdur_O-S-H
- AND BT_Interactions O-S-H=manybtint_O-S-H
- AND SMS received O-S-H=manysmsrec_O-S-H</t>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND SMS sent O-S-H=manysmssent_O-S-H</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS conversation O-S-H=manysmsconv_O-S-H
- AND SMS sent O-S-H=manysmssent_O-S-H</t>
+          <t>Calls Duration O-S-H=veryhighcalldur_O-S-H</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0.0505952380952381</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8500000000000001</v>
+        <v>0.5074626865671642</v>
       </c>
       <c r="E8" t="n">
-        <v>9.681355932203392</v>
+        <v>4.371986222732492</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04536918934240363</v>
+        <v>0.03902264030612244</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>34</v>
@@ -721,35 +704,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS conversation O-S-H=manysmsconv_O-S-H
- AND SMS sent O-S-H=manysmssent_O-S-H</t>
+          <t>BT_Interactions O-S-H=manybtint_O-S-H
+ AND SMS unique people O-S-H=manysmsunq_O-S-H</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BT_Average Duration O-S-H=middlebtavgdur_O-S-H
- AND BT_Interactions O-S-H=manybtint_O-S-H
- AND SMS received O-S-H=manysmsrec_O-S-H</t>
+          <t>fb=verymanyfb</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0.0505952380952381</v>
       </c>
       <c r="D9" t="n">
-        <v>0.576271186440678</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="E9" t="n">
-        <v>9.68135593220339</v>
+        <v>4.350342726580351</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04536918934240363</v>
+        <v>0.03896506519274377</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>34</v>
@@ -759,67 +739,65 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS received S-H=manysmsrec_S-H</t>
+ AND SMS unique people O-S-H=manysmsunq_O-S-H</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SMS conversation S-H=manysmsconv_S-H
- AND SMS sent S-H=manysmssent_S-H</t>
+          <t>fb=verymanyfb</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0505952380952381</v>
+        <v>0.05208333333333334</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8500000000000001</v>
+        <v>0.6140350877192983</v>
       </c>
       <c r="E10" t="n">
-        <v>9.520000000000001</v>
+        <v>4.085461177696717</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04528061224489796</v>
+        <v>0.03933487457482993</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMS conversation S-H=manysmsconv_S-H
- AND SMS sent S-H=manysmssent_S-H</t>
+          <t>BT_Unique people O-S-H=manybtunq_O-S-H
+ AND Calls Duration O-S-H=veryhighcalldur_O-S-H</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BT_Unique people O-S-H=manybtunq_O-S-H
- AND SMS received S-H=manysmsrec_S-H</t>
+          <t>SMS conversation S-H=manysmsconv_S-H</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0.0505952380952381</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="E11" t="n">
-        <v>9.52</v>
+        <v>3.958419958419959</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04528061224489796</v>
+        <v>0.03781356292517007</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>34</v>
